--- a/artfynd/A 57467-2025 artfynd.xlsx
+++ b/artfynd/A 57467-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138183</v>
+        <v>126024695</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422081</v>
+        <v>422117</v>
       </c>
       <c r="R2" t="n">
-        <v>6586335</v>
+        <v>6586354</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138097</v>
+        <v>124138183</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422122</v>
+        <v>422081</v>
       </c>
       <c r="R3" t="n">
-        <v>6586371</v>
+        <v>6586335</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126024661</v>
+        <v>124138097</v>
       </c>
       <c r="B4" t="n">
-        <v>91210</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422117</v>
+        <v>422122</v>
       </c>
       <c r="R4" t="n">
-        <v>6586354</v>
+        <v>6586371</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -944,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126024695</v>
+        <v>126024661</v>
       </c>
       <c r="B5" t="n">
-        <v>96614</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,7 +1007,7 @@
         <v>6586354</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 57467-2025 artfynd.xlsx
+++ b/artfynd/A 57467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126024695</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138183</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138097</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126024661</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>